--- a/business_forms/034_project_task_delegation_request_form--business_forms.xlsx
+++ b/business_forms/034_project_task_delegation_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_task_delegation_request_form</t>
+          <t>project_manager_id</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>project_task_delegation_request</t>
+          <t>Project Manager ID</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_manager_id</t>
+          <t>task_id</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>project_manager</t>
+          <t>Task ID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>task_id</t>
+          <t>assignee_id</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>Assignee ID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assignee_id</t>
+          <t>assigned_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assignee</t>
+          <t>Assigned Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_date</t>
+          <t>assigned_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>assigned_date</t>
+          <t>Assigned Time</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_time</t>
+          <t>assigned_by</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_time</t>
+          <t>Assigned By</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assigned_by</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>assigned_by</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>assigned_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Assigned Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_status</t>
+          <t>reason_for_re_assignment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_status</t>
+          <t>Reason for Re-Assignment</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reason_for_re_assignment</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reason_for_re_assignment</t>
+          <t>Assigned To</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>Assigned To Status</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>assigned_by_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Assigned By Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assigned_by_status</t>
+          <t>assigned_to_status_reason</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assigned_by_status</t>
+          <t>Assigned To Status Reason</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_by_status_reason</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>assigned_by_status_reason</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>task_details</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Task Details</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>task_details</t>
+          <t>assigned_to_status_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>task_details</t>
+          <t>Assigned To Status 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>assigned_to_status</t>
+          <t>assigned_by_status_reason</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>assigned_to_status</t>
+          <t>Assigned By Status Reason</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_to_status_reason</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>assigned_to_status_reason</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_to_status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>assigned_to_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>assigned_by_status</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>assigned_by_status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'not_assigned'}</t>
+          <t>not_assigned</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Not Assigned'}</t>
+          <t>Not Assigned</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'assigned'}</t>
+          <t>assigned</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Assigned'}</t>
+          <t>Assigned</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'re-proposed'}</t>
+          <t>re-proposed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Re-proposed'}</t>
+          <t>Re-Proposed</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_1'}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 1'}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_2'}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 2'}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_3'}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 3'}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_4'}</t>
+          <t>team_member_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 4'}</t>
+          <t>Team Member 4</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_5'}</t>
+          <t>team_member_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 5'}</t>
+          <t>Team Member 5</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_6'}</t>
+          <t>team_member_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 6'}</t>
+          <t>Team Member 6</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_7'}</t>
+          <t>team_member_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 7'}</t>
+          <t>Team Member 7</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_8'}</t>
+          <t>team_member_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 8'}</t>
+          <t>Team Member 8</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_9'}</t>
+          <t>team_member_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 9'}</t>
+          <t>Team Member 9</t>
         </is>
       </c>
     </row>
@@ -1352,80 +1191,80 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_10'}</t>
+          <t>team_member_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 10'}</t>
+          <t>Team Member 10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'on_leave'}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'On Leave'}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'on_vacation'}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'On Vacation'}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>team_member_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Team Member 4</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_1'}</t>
+          <t>team_member_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 1'}</t>
+          <t>Team Member 5</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_2'}</t>
+          <t>team_member_6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 2'}</t>
+          <t>Team Member 6</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_3'}</t>
+          <t>team_member_7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 3'}</t>
+          <t>Team Member 7</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_4'}</t>
+          <t>team_member_8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 4'}</t>
+          <t>Team Member 8</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_5'}</t>
+          <t>team_member_9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 5'}</t>
+          <t>Team Member 9</t>
         </is>
       </c>
     </row>
@@ -1539,709 +1378,454 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_6'}</t>
+          <t>team_member_10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 6'}</t>
+          <t>Team Member 10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_by_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_7'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 7'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_by_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_8'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 8'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_by_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_9'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 9'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_by_status_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_10'}</t>
+          <t>on_vacation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 10'}</t>
+          <t>On Vacation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_1'}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 1'}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_2'}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 2'}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_3'}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 3'}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_4'}</t>
+          <t>team_member_4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 4'}</t>
+          <t>Team Member 4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_5'}</t>
+          <t>team_member_5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 5'}</t>
+          <t>Team Member 5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_6'}</t>
+          <t>team_member_6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 6'}</t>
+          <t>Team Member 6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_7'}</t>
+          <t>team_member_7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 7'}</t>
+          <t>Team Member 7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_8'}</t>
+          <t>team_member_8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 8'}</t>
+          <t>Team Member 8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_9'}</t>
+          <t>team_member_9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 9'}</t>
+          <t>Team Member 9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>assigned_to_status_choices</t>
+          <t>assigned_to_status_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_10'}</t>
+          <t>team_member_10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 10'}</t>
+          <t>Team Member 10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'on_leave'}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'On Leave'}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>assigned_by_status_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'on_vacation'}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'On Vacation'}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>team_member_4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Team Member 4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_1'}</t>
+          <t>team_member_5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 1'}</t>
+          <t>Team Member 5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_2'}</t>
+          <t>team_member_6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 2'}</t>
+          <t>Team Member 6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_3'}</t>
+          <t>team_member_7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 3'}</t>
+          <t>Team Member 7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_4'}</t>
+          <t>team_member_8</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 4'}</t>
+          <t>Team Member 8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_5'}</t>
+          <t>team_member_9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 5'}</t>
+          <t>Team Member 9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'team_member_6'}</t>
+          <t>team_member_10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member 6'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_7'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 7'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_8'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 8'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_9'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 9'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_10'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 10'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'value':_'not_applicable'}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'value': 'Not Applicable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_1'}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_2'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_3'}</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_4'}</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_5'}</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_6'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 6'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_7'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 7'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_8'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 8'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_9'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 9'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'value':_'team_member_10'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'value': 'Team Member 10'}</t>
+          <t>Team Member 10</t>
         </is>
       </c>
     </row>
